--- a/Practica 5 - Grupo 4/Databases/recruitment_applicants_2023.xlsx
+++ b/Practica 5 - Grupo 4/Databases/recruitment_applicants_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daisung/Google Drive/Documents/UQ/PHRA book/R Version/Data and code/Ch 8/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fb339acf2833aae4/Documentos/GitHub/Practicas-PA/Practica 5 - Grupo 4/Databases/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D83605CD-1DD5-0D44-9FFE-9C3FE5C56936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D83605CD-1DD5-0D44-9FFE-9C3FE5C56936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13EBC8B8-30EF-46D9-9C9A-9DE195E44ACF}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="29060" windowWidth="51200" windowHeight="28540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -449,9 +449,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I281"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="4" max="4" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="26.453125" customWidth="1"/>
+    <col min="6" max="6" width="15.90625" customWidth="1"/>
+    <col min="7" max="7" width="9.54296875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,7 +486,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -509,7 +515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -538,7 +544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -567,7 +573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -596,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -621,7 +627,7 @@
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -646,7 +652,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -671,7 +677,7 @@
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -696,7 +702,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -721,7 +727,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -742,7 +748,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -763,7 +769,7 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -784,7 +790,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -805,7 +811,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -826,7 +832,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -847,7 +853,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -868,7 +874,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -889,7 +895,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -910,7 +916,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -931,7 +937,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -960,7 +966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -989,7 +995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1043,7 +1049,7 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1068,7 +1074,7 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1097,7 +1103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1126,7 +1132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1151,7 +1157,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1172,7 +1178,7 @@
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1193,7 +1199,7 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1218,7 +1224,7 @@
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1243,7 +1249,7 @@
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1268,7 +1274,7 @@
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -1293,7 +1299,7 @@
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1318,7 +1324,7 @@
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -1343,7 +1349,7 @@
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1368,7 +1374,7 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1393,7 +1399,7 @@
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1418,7 +1424,7 @@
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -1443,7 +1449,7 @@
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1468,7 +1474,7 @@
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1493,7 +1499,7 @@
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -1514,7 +1520,7 @@
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1535,7 +1541,7 @@
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1556,7 +1562,7 @@
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1577,7 +1583,7 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -1598,7 +1604,7 @@
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -1619,7 +1625,7 @@
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -1640,7 +1646,7 @@
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -1661,7 +1667,7 @@
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -1682,7 +1688,7 @@
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -1703,7 +1709,7 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -1724,7 +1730,7 @@
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -1745,7 +1751,7 @@
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -1766,7 +1772,7 @@
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -1787,7 +1793,7 @@
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -1808,7 +1814,7 @@
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -1829,7 +1835,7 @@
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -1850,7 +1856,7 @@
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -1871,7 +1877,7 @@
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -1892,7 +1898,7 @@
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -1913,7 +1919,7 @@
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -1934,7 +1940,7 @@
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -1955,7 +1961,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -1976,7 +1982,7 @@
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -1997,7 +2003,7 @@
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2018,7 +2024,7 @@
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -2039,7 +2045,7 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2060,7 +2066,7 @@
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -2081,7 +2087,7 @@
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2102,7 +2108,7 @@
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -2123,7 +2129,7 @@
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2144,7 +2150,7 @@
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -2165,7 +2171,7 @@
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2186,7 +2192,7 @@
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -2207,7 +2213,7 @@
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -2228,7 +2234,7 @@
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -2249,7 +2255,7 @@
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -2270,7 +2276,7 @@
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -2291,7 +2297,7 @@
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -2312,7 +2318,7 @@
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -2333,7 +2339,7 @@
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -2354,7 +2360,7 @@
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -2375,7 +2381,7 @@
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -2396,7 +2402,7 @@
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -2417,7 +2423,7 @@
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -2438,7 +2444,7 @@
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -2459,7 +2465,7 @@
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -2480,7 +2486,7 @@
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -2501,7 +2507,7 @@
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -2522,7 +2528,7 @@
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -2543,7 +2549,7 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -2564,7 +2570,7 @@
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -2585,7 +2591,7 @@
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -2606,7 +2612,7 @@
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -2627,7 +2633,7 @@
       <c r="H96" s="1"/>
       <c r="I96" s="1"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -2648,7 +2654,7 @@
       <c r="H97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -2669,7 +2675,7 @@
       <c r="H98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -2690,7 +2696,7 @@
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -2711,7 +2717,7 @@
       <c r="H100" s="1"/>
       <c r="I100" s="1"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -2732,7 +2738,7 @@
       <c r="H101" s="1"/>
       <c r="I101" s="1"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -2753,7 +2759,7 @@
       <c r="H102" s="1"/>
       <c r="I102" s="1"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -2774,7 +2780,7 @@
       <c r="H103" s="1"/>
       <c r="I103" s="1"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -2795,7 +2801,7 @@
       <c r="H104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -2816,7 +2822,7 @@
       <c r="H105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -2837,7 +2843,7 @@
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -2858,7 +2864,7 @@
       <c r="H107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -2879,7 +2885,7 @@
       <c r="H108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -2900,7 +2906,7 @@
       <c r="H109" s="1"/>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -2921,7 +2927,7 @@
       <c r="H110" s="1"/>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -2942,7 +2948,7 @@
       <c r="H111" s="1"/>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -2963,7 +2969,7 @@
       <c r="H112" s="1"/>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -2984,7 +2990,7 @@
       <c r="H113" s="1"/>
       <c r="I113" s="1"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -3005,7 +3011,7 @@
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -3026,7 +3032,7 @@
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -3047,7 +3053,7 @@
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -3068,7 +3074,7 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -3089,7 +3095,7 @@
       <c r="H118" s="1"/>
       <c r="I118" s="1"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -3110,7 +3116,7 @@
       <c r="H119" s="1"/>
       <c r="I119" s="1"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -3131,7 +3137,7 @@
       <c r="H120" s="1"/>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -3152,7 +3158,7 @@
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -3173,7 +3179,7 @@
       <c r="H122" s="1"/>
       <c r="I122" s="1"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -3194,7 +3200,7 @@
       <c r="H123" s="1"/>
       <c r="I123" s="1"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -3215,7 +3221,7 @@
       <c r="H124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -3236,7 +3242,7 @@
       <c r="H125" s="1"/>
       <c r="I125" s="1"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -3257,7 +3263,7 @@
       <c r="H126" s="1"/>
       <c r="I126" s="1"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -3278,7 +3284,7 @@
       <c r="H127" s="1"/>
       <c r="I127" s="1"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -3299,7 +3305,7 @@
       <c r="H128" s="1"/>
       <c r="I128" s="1"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -3320,7 +3326,7 @@
       <c r="H129" s="1"/>
       <c r="I129" s="1"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -3341,7 +3347,7 @@
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -3362,7 +3368,7 @@
       <c r="H131" s="1"/>
       <c r="I131" s="1"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -3383,7 +3389,7 @@
       <c r="H132" s="1"/>
       <c r="I132" s="1"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -3404,7 +3410,7 @@
       <c r="H133" s="1"/>
       <c r="I133" s="1"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -3425,7 +3431,7 @@
       <c r="H134" s="1"/>
       <c r="I134" s="1"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -3446,7 +3452,7 @@
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -3467,7 +3473,7 @@
       <c r="H136" s="1"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -3488,7 +3494,7 @@
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -3509,7 +3515,7 @@
       <c r="H138" s="1"/>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -3530,7 +3536,7 @@
       <c r="H139" s="1"/>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -3551,7 +3557,7 @@
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -3572,7 +3578,7 @@
       <c r="H141" s="1"/>
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -3601,7 +3607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -3630,7 +3636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -3659,7 +3665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -3688,7 +3694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -3717,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -3746,7 +3752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -3775,7 +3781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -3804,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -3829,7 +3835,7 @@
       <c r="H150" s="1"/>
       <c r="I150" s="1"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -3858,7 +3864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -3887,7 +3893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -3916,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -3970,7 +3976,7 @@
       <c r="H155" s="1"/>
       <c r="I155" s="1"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -3999,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -4028,7 +4034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -4053,7 +4059,7 @@
       <c r="H158" s="1"/>
       <c r="I158" s="1"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -4078,7 +4084,7 @@
       <c r="H159" s="1"/>
       <c r="I159" s="1"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -4099,7 +4105,7 @@
       <c r="H160" s="1"/>
       <c r="I160" s="1"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -4128,7 +4134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -4157,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -4211,7 +4217,7 @@
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -4236,7 +4242,7 @@
       <c r="H165" s="1"/>
       <c r="I165" s="1"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -4265,7 +4271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -4294,7 +4300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -4319,7 +4325,7 @@
       <c r="H168" s="1"/>
       <c r="I168" s="1"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -4340,7 +4346,7 @@
       <c r="H169" s="1"/>
       <c r="I169" s="1"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -4361,7 +4367,7 @@
       <c r="H170" s="1"/>
       <c r="I170" s="1"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -4382,7 +4388,7 @@
       <c r="H171" s="1"/>
       <c r="I171" s="1"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -4403,7 +4409,7 @@
       <c r="H172" s="1"/>
       <c r="I172" s="1"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A173" s="2">
         <v>172</v>
       </c>
@@ -4424,7 +4430,7 @@
       <c r="H173" s="1"/>
       <c r="I173" s="1"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -4445,7 +4451,7 @@
       <c r="H174" s="1"/>
       <c r="I174" s="1"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A175" s="2">
         <v>174</v>
       </c>
@@ -4466,7 +4472,7 @@
       <c r="H175" s="1"/>
       <c r="I175" s="1"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -4487,7 +4493,7 @@
       <c r="H176" s="1"/>
       <c r="I176" s="1"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A177" s="2">
         <v>176</v>
       </c>
@@ -4508,7 +4514,7 @@
       <c r="H177" s="1"/>
       <c r="I177" s="1"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -4529,7 +4535,7 @@
       <c r="H178" s="1"/>
       <c r="I178" s="1"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A179" s="2">
         <v>178</v>
       </c>
@@ -4550,7 +4556,7 @@
       <c r="H179" s="1"/>
       <c r="I179" s="1"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -4571,7 +4577,7 @@
       <c r="H180" s="1"/>
       <c r="I180" s="1"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A181" s="2">
         <v>180</v>
       </c>
@@ -4592,7 +4598,7 @@
       <c r="H181" s="1"/>
       <c r="I181" s="1"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -4613,7 +4619,7 @@
       <c r="H182" s="1"/>
       <c r="I182" s="1"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A183" s="2">
         <v>182</v>
       </c>
@@ -4634,7 +4640,7 @@
       <c r="H183" s="1"/>
       <c r="I183" s="1"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -4655,7 +4661,7 @@
       <c r="H184" s="1"/>
       <c r="I184" s="1"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A185" s="2">
         <v>184</v>
       </c>
@@ -4676,7 +4682,7 @@
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -4697,7 +4703,7 @@
       <c r="H186" s="1"/>
       <c r="I186" s="1"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A187" s="2">
         <v>186</v>
       </c>
@@ -4718,7 +4724,7 @@
       <c r="H187" s="1"/>
       <c r="I187" s="1"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -4739,7 +4745,7 @@
       <c r="H188" s="1"/>
       <c r="I188" s="1"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A189" s="2">
         <v>188</v>
       </c>
@@ -4760,7 +4766,7 @@
       <c r="H189" s="1"/>
       <c r="I189" s="1"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -4781,7 +4787,7 @@
       <c r="H190" s="1"/>
       <c r="I190" s="1"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A191" s="2">
         <v>190</v>
       </c>
@@ -4802,7 +4808,7 @@
       <c r="H191" s="1"/>
       <c r="I191" s="1"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -4823,7 +4829,7 @@
       <c r="H192" s="1"/>
       <c r="I192" s="1"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A193" s="2">
         <v>192</v>
       </c>
@@ -4844,7 +4850,7 @@
       <c r="H193" s="1"/>
       <c r="I193" s="1"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -4865,7 +4871,7 @@
       <c r="H194" s="1"/>
       <c r="I194" s="1"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A195" s="2">
         <v>194</v>
       </c>
@@ -4886,7 +4892,7 @@
       <c r="H195" s="1"/>
       <c r="I195" s="1"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -4907,7 +4913,7 @@
       <c r="H196" s="1"/>
       <c r="I196" s="1"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A197" s="2">
         <v>196</v>
       </c>
@@ -4928,7 +4934,7 @@
       <c r="H197" s="1"/>
       <c r="I197" s="1"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -4949,7 +4955,7 @@
       <c r="H198" s="1"/>
       <c r="I198" s="1"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A199" s="2">
         <v>198</v>
       </c>
@@ -4970,7 +4976,7 @@
       <c r="H199" s="1"/>
       <c r="I199" s="1"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -4991,7 +4997,7 @@
       <c r="H200" s="1"/>
       <c r="I200" s="1"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A201" s="2">
         <v>200</v>
       </c>
@@ -5012,7 +5018,7 @@
       <c r="H201" s="1"/>
       <c r="I201" s="1"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -5033,7 +5039,7 @@
       <c r="H202" s="1"/>
       <c r="I202" s="1"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A203" s="2">
         <v>202</v>
       </c>
@@ -5054,7 +5060,7 @@
       <c r="H203" s="1"/>
       <c r="I203" s="1"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -5075,7 +5081,7 @@
       <c r="H204" s="1"/>
       <c r="I204" s="1"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A205" s="2">
         <v>204</v>
       </c>
@@ -5096,7 +5102,7 @@
       <c r="H205" s="1"/>
       <c r="I205" s="1"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -5117,7 +5123,7 @@
       <c r="H206" s="1"/>
       <c r="I206" s="1"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A207" s="2">
         <v>206</v>
       </c>
@@ -5138,7 +5144,7 @@
       <c r="H207" s="1"/>
       <c r="I207" s="1"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -5159,7 +5165,7 @@
       <c r="H208" s="1"/>
       <c r="I208" s="1"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A209" s="2">
         <v>208</v>
       </c>
@@ -5180,7 +5186,7 @@
       <c r="H209" s="1"/>
       <c r="I209" s="1"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -5201,7 +5207,7 @@
       <c r="H210" s="1"/>
       <c r="I210" s="1"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A211" s="2">
         <v>210</v>
       </c>
@@ -5222,7 +5228,7 @@
       <c r="H211" s="1"/>
       <c r="I211" s="1"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -5243,7 +5249,7 @@
       <c r="H212" s="1"/>
       <c r="I212" s="1"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A213" s="2">
         <v>212</v>
       </c>
@@ -5264,7 +5270,7 @@
       <c r="H213" s="1"/>
       <c r="I213" s="1"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -5285,7 +5291,7 @@
       <c r="H214" s="1"/>
       <c r="I214" s="1"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A215" s="2">
         <v>214</v>
       </c>
@@ -5306,7 +5312,7 @@
       <c r="H215" s="1"/>
       <c r="I215" s="1"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -5327,7 +5333,7 @@
       <c r="H216" s="1"/>
       <c r="I216" s="1"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A217" s="2">
         <v>216</v>
       </c>
@@ -5348,7 +5354,7 @@
       <c r="H217" s="1"/>
       <c r="I217" s="1"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -5369,7 +5375,7 @@
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A219" s="2">
         <v>218</v>
       </c>
@@ -5390,7 +5396,7 @@
       <c r="H219" s="1"/>
       <c r="I219" s="1"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -5411,7 +5417,7 @@
       <c r="H220" s="1"/>
       <c r="I220" s="1"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A221" s="2">
         <v>220</v>
       </c>
@@ -5432,7 +5438,7 @@
       <c r="H221" s="1"/>
       <c r="I221" s="1"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -5453,7 +5459,7 @@
       <c r="H222" s="1"/>
       <c r="I222" s="1"/>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A223" s="2">
         <v>222</v>
       </c>
@@ -5474,7 +5480,7 @@
       <c r="H223" s="1"/>
       <c r="I223" s="1"/>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -5495,7 +5501,7 @@
       <c r="H224" s="1"/>
       <c r="I224" s="1"/>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A225" s="2">
         <v>224</v>
       </c>
@@ -5516,7 +5522,7 @@
       <c r="H225" s="1"/>
       <c r="I225" s="1"/>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -5537,7 +5543,7 @@
       <c r="H226" s="1"/>
       <c r="I226" s="1"/>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A227" s="2">
         <v>226</v>
       </c>
@@ -5558,7 +5564,7 @@
       <c r="H227" s="1"/>
       <c r="I227" s="1"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -5579,7 +5585,7 @@
       <c r="H228" s="1"/>
       <c r="I228" s="1"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A229" s="2">
         <v>228</v>
       </c>
@@ -5600,7 +5606,7 @@
       <c r="H229" s="1"/>
       <c r="I229" s="1"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -5621,7 +5627,7 @@
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A231" s="2">
         <v>230</v>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="H231" s="1"/>
       <c r="I231" s="1"/>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -5663,7 +5669,7 @@
       <c r="H232" s="1"/>
       <c r="I232" s="1"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A233" s="2">
         <v>232</v>
       </c>
@@ -5684,7 +5690,7 @@
       <c r="H233" s="1"/>
       <c r="I233" s="1"/>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -5705,7 +5711,7 @@
       <c r="H234" s="1"/>
       <c r="I234" s="1"/>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A235" s="2">
         <v>234</v>
       </c>
@@ -5726,7 +5732,7 @@
       <c r="H235" s="1"/>
       <c r="I235" s="1"/>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -5747,7 +5753,7 @@
       <c r="H236" s="1"/>
       <c r="I236" s="1"/>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A237" s="2">
         <v>236</v>
       </c>
@@ -5768,7 +5774,7 @@
       <c r="H237" s="1"/>
       <c r="I237" s="1"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -5789,7 +5795,7 @@
       <c r="H238" s="1"/>
       <c r="I238" s="1"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A239" s="2">
         <v>238</v>
       </c>
@@ -5810,7 +5816,7 @@
       <c r="H239" s="1"/>
       <c r="I239" s="1"/>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -5831,7 +5837,7 @@
       <c r="H240" s="1"/>
       <c r="I240" s="1"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A241" s="2">
         <v>240</v>
       </c>
@@ -5852,7 +5858,7 @@
       <c r="H241" s="1"/>
       <c r="I241" s="1"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -5873,7 +5879,7 @@
       <c r="H242" s="1"/>
       <c r="I242" s="1"/>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A243" s="2">
         <v>242</v>
       </c>
@@ -5894,7 +5900,7 @@
       <c r="H243" s="1"/>
       <c r="I243" s="1"/>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -5915,7 +5921,7 @@
       <c r="H244" s="1"/>
       <c r="I244" s="1"/>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A245" s="2">
         <v>244</v>
       </c>
@@ -5936,7 +5942,7 @@
       <c r="H245" s="1"/>
       <c r="I245" s="1"/>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -5957,7 +5963,7 @@
       <c r="H246" s="1"/>
       <c r="I246" s="1"/>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A247" s="2">
         <v>246</v>
       </c>
@@ -5978,7 +5984,7 @@
       <c r="H247" s="1"/>
       <c r="I247" s="1"/>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -5999,7 +6005,7 @@
       <c r="H248" s="1"/>
       <c r="I248" s="1"/>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A249" s="2">
         <v>248</v>
       </c>
@@ -6020,7 +6026,7 @@
       <c r="H249" s="1"/>
       <c r="I249" s="1"/>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A250" s="2">
         <v>249</v>
       </c>
@@ -6041,7 +6047,7 @@
       <c r="H250" s="1"/>
       <c r="I250" s="1"/>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A251" s="2">
         <v>250</v>
       </c>
@@ -6062,7 +6068,7 @@
       <c r="H251" s="1"/>
       <c r="I251" s="1"/>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A252" s="2">
         <v>251</v>
       </c>
@@ -6083,7 +6089,7 @@
       <c r="H252" s="1"/>
       <c r="I252" s="1"/>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A253" s="2">
         <v>252</v>
       </c>
@@ -6104,7 +6110,7 @@
       <c r="H253" s="1"/>
       <c r="I253" s="1"/>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A254" s="2">
         <v>253</v>
       </c>
@@ -6125,7 +6131,7 @@
       <c r="H254" s="1"/>
       <c r="I254" s="1"/>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A255" s="2">
         <v>254</v>
       </c>
@@ -6146,7 +6152,7 @@
       <c r="H255" s="1"/>
       <c r="I255" s="1"/>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -6167,7 +6173,7 @@
       <c r="H256" s="1"/>
       <c r="I256" s="1"/>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A257" s="2">
         <v>256</v>
       </c>
@@ -6188,7 +6194,7 @@
       <c r="H257" s="1"/>
       <c r="I257" s="1"/>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A258" s="2">
         <v>257</v>
       </c>
@@ -6209,7 +6215,7 @@
       <c r="H258" s="1"/>
       <c r="I258" s="1"/>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A259" s="2">
         <v>258</v>
       </c>
@@ -6230,7 +6236,7 @@
       <c r="H259" s="1"/>
       <c r="I259" s="1"/>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A260" s="2">
         <v>259</v>
       </c>
@@ -6251,7 +6257,7 @@
       <c r="H260" s="1"/>
       <c r="I260" s="1"/>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A261" s="2">
         <v>260</v>
       </c>
@@ -6272,7 +6278,7 @@
       <c r="H261" s="1"/>
       <c r="I261" s="1"/>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A262" s="2">
         <v>261</v>
       </c>
@@ -6293,7 +6299,7 @@
       <c r="H262" s="1"/>
       <c r="I262" s="1"/>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A263" s="2">
         <v>262</v>
       </c>
@@ -6314,7 +6320,7 @@
       <c r="H263" s="1"/>
       <c r="I263" s="1"/>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A264" s="2">
         <v>263</v>
       </c>
@@ -6335,7 +6341,7 @@
       <c r="H264" s="1"/>
       <c r="I264" s="1"/>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A265" s="2">
         <v>264</v>
       </c>
@@ -6356,7 +6362,7 @@
       <c r="H265" s="1"/>
       <c r="I265" s="1"/>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -6377,7 +6383,7 @@
       <c r="H266" s="1"/>
       <c r="I266" s="1"/>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A267" s="2">
         <v>266</v>
       </c>
@@ -6398,7 +6404,7 @@
       <c r="H267" s="1"/>
       <c r="I267" s="1"/>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -6419,7 +6425,7 @@
       <c r="H268" s="1"/>
       <c r="I268" s="1"/>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A269" s="2">
         <v>268</v>
       </c>
@@ -6440,7 +6446,7 @@
       <c r="H269" s="1"/>
       <c r="I269" s="1"/>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -6461,7 +6467,7 @@
       <c r="H270" s="1"/>
       <c r="I270" s="1"/>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A271" s="2">
         <v>270</v>
       </c>
@@ -6482,7 +6488,7 @@
       <c r="H271" s="1"/>
       <c r="I271" s="1"/>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -6503,7 +6509,7 @@
       <c r="H272" s="1"/>
       <c r="I272" s="1"/>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A273" s="2">
         <v>272</v>
       </c>
@@ -6524,7 +6530,7 @@
       <c r="H273" s="1"/>
       <c r="I273" s="1"/>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -6545,7 +6551,7 @@
       <c r="H274" s="1"/>
       <c r="I274" s="1"/>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A275" s="2">
         <v>274</v>
       </c>
@@ -6566,7 +6572,7 @@
       <c r="H275" s="1"/>
       <c r="I275" s="1"/>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -6587,7 +6593,7 @@
       <c r="H276" s="1"/>
       <c r="I276" s="1"/>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A277" s="2">
         <v>276</v>
       </c>
@@ -6608,7 +6614,7 @@
       <c r="H277" s="1"/>
       <c r="I277" s="1"/>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -6629,7 +6635,7 @@
       <c r="H278" s="1"/>
       <c r="I278" s="1"/>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A279" s="2">
         <v>278</v>
       </c>
@@ -6650,7 +6656,7 @@
       <c r="H279" s="1"/>
       <c r="I279" s="1"/>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -6671,7 +6677,7 @@
       <c r="H280" s="1"/>
       <c r="I280" s="1"/>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A281" s="2">
         <v>280</v>
       </c>
@@ -6701,13 +6707,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD034104-864F-9E42-92A4-65AA18E9A521}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -6718,7 +6724,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6726,7 +6732,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -6737,7 +6743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6759,7 +6765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -6770,7 +6776,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -6781,7 +6787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6792,7 +6798,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -6803,7 +6809,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
